--- a/data/estimates/608-macon-habitat-estimate-corrected.xlsx
+++ b/data/estimates/608-macon-habitat-estimate-corrected.xlsx
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Source: Booker+Vick permit set A2.2 (May 2026) · 1425 SF heated · Prepared 2026-06-08</t>
+          <t>Source: Booker+Vick permit set A2.2 (May 2026) · 1425 SF heated · Prepared 2026-06-17</t>
         </is>
       </c>
     </row>
